--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260917.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,983,288</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>1,983,288</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,379,296</t>
+          <t>139,482</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>139,482</t>
+          <t>5,379,296</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>849,349</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>849,349</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,670,000</t>
+          <t>372,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,816,000</t>
+          <t>5,670,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>372,000</t>
+          <t>1,816,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,186,441</t>
+          <t>3,449,981</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,449,981</t>
+          <t>1,186,441</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,366,384</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>1,366,384</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,171,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,171,107</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>317,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>769,000</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>769,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>4,915,956</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>4,915,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>994,121</t>
+          <t>1,742,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,742,000</t>
+          <t>994,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
